--- a/output/models and plots/abund_best_models.xlsx
+++ b/output/models and plots/abund_best_models.xlsx
@@ -428,6 +428,12 @@
       <c r="D2">
         <v>-470.0889160031538</v>
       </c>
+      <c r="E2">
+        <v>0.1410431627488576</v>
+      </c>
+      <c r="F2">
+        <v>0.1410431653802087</v>
+      </c>
       <c r="G2">
         <v>94</v>
       </c>
@@ -461,6 +467,12 @@
       <c r="D3">
         <v>-469.5267223569962</v>
       </c>
+      <c r="E3">
+        <v>0.15020877837859</v>
+      </c>
+      <c r="F3">
+        <v>0.1502087800200186</v>
+      </c>
       <c r="G3">
         <v>93</v>
       </c>
@@ -494,6 +506,12 @@
       <c r="D4">
         <v>-469.5664836154454</v>
       </c>
+      <c r="E4">
+        <v>0.1503454336370946</v>
+      </c>
+      <c r="F4">
+        <v>0.1503454359651413</v>
+      </c>
       <c r="G4">
         <v>93</v>
       </c>
@@ -526,6 +544,12 @@
       </c>
       <c r="D5">
         <v>-469.6926147946568</v>
+      </c>
+      <c r="E5">
+        <v>0.1445069163394255</v>
+      </c>
+      <c r="F5">
+        <v>0.1445069183882031</v>
       </c>
       <c r="G5">
         <v>93</v>

--- a/output/models and plots/abund_best_models.xlsx
+++ b/output/models and plots/abund_best_models.xlsx
@@ -1,21 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB85D2E-F49E-8545-87C5-45E50C2821BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>AICc</t>
+  </si>
+  <si>
+    <t>LL</t>
+  </si>
+  <si>
+    <t>mR2</t>
+  </si>
+  <si>
+    <t>cR2</t>
+  </si>
+  <si>
+    <t>RDF</t>
+  </si>
+  <si>
+    <t>adjAICc</t>
+  </si>
+  <si>
+    <t>deltaAICc</t>
+  </si>
+  <si>
+    <t>delta_adjAICc</t>
+  </si>
+  <si>
+    <t>total_abundance ~ bait + canopy + (1 | location)</t>
+  </si>
+  <si>
+    <t>total_abundance ~ bait + depth + canopy + (1 | location)</t>
+  </si>
+  <si>
+    <t>total_abundance ~ bait + scytothalia + ecklonia + (1 | location)</t>
+  </si>
+  <si>
+    <t>total_abundance ~ bait + mean_relief + canopy + (1 | location)</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>No. Par</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,24 +109,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +174,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +208,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +243,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,221 +419,174 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="48.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>predictors</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AICc</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LL</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mR2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cR2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>RDF</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>n_predictors</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>adjAICc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>deltaAICc</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>delta_adjAICc</t>
-        </is>
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>total_abundance ~ bait + canopy + (1 | location)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>canopy</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>953.0810578127591</v>
-      </c>
-      <c r="D2">
-        <v>-470.0889160031538</v>
-      </c>
-      <c r="E2">
-        <v>0.1410431627488576</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2">
+        <v>953.08105781275913</v>
+      </c>
+      <c r="C2" s="2">
+        <v>-470.08891600315383</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.14104316274885759</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.1410431653802087</v>
       </c>
       <c r="F2">
-        <v>0.1410431653802087</v>
+        <v>94</v>
       </c>
       <c r="G2">
-        <v>94</v>
-      </c>
-      <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>955.0810578127591</v>
-      </c>
-      <c r="J2">
+      <c r="H2" s="3">
+        <v>955.08105781275913</v>
+      </c>
+      <c r="I2" s="3">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="J2" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>total_abundance ~ bait + depth + canopy + (1 | location)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>depth + canopy</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>954.2708360183402</v>
-      </c>
-      <c r="D3">
-        <v>-469.5267223569962</v>
-      </c>
-      <c r="E3">
-        <v>0.15020877837859</v>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2">
+        <v>954.27083601834022</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-469.52672235699617</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.15020877837859001</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.15020878002001861</v>
       </c>
       <c r="F3">
-        <v>0.1502087800200186</v>
+        <v>93</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3">
+        <v>958.27083601834022</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1.1897782055810919</v>
+      </c>
+      <c r="J3" s="3">
+        <v>3.1897782055810922</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2">
+        <v>954.35035853523868</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-469.56648361544541</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.1503454336370946</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.1503454359651413</v>
+      </c>
+      <c r="F4">
         <v>93</v>
       </c>
-      <c r="H3">
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="I3">
-        <v>958.2708360183402</v>
-      </c>
-      <c r="J3">
-        <v>1.189778205581092</v>
-      </c>
-      <c r="K3">
-        <v>3.189778205581092</v>
+      <c r="H4" s="3">
+        <v>958.35035853523868</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1.2693007224795561</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3.2693007224795561</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>total_abundance ~ bait + scytothalia + ecklonia + (1 | location)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>scytothalia + ecklonia</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>954.3503585352387</v>
-      </c>
-      <c r="D4">
-        <v>-469.5664836154454</v>
-      </c>
-      <c r="E4">
-        <v>0.1503454336370946</v>
-      </c>
-      <c r="F4">
-        <v>0.1503454359651413</v>
-      </c>
-      <c r="G4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>954.60262089366142</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-469.69261479465678</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.1445069163394255</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.14450691838820309</v>
+      </c>
+      <c r="F5">
         <v>93</v>
       </c>
-      <c r="H4">
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="I4">
-        <v>958.3503585352387</v>
-      </c>
-      <c r="J4">
-        <v>1.269300722479556</v>
-      </c>
-      <c r="K4">
-        <v>3.269300722479556</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>total_abundance ~ bait + mean_relief + canopy + (1 | location)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean_relief + canopy</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>954.6026208936614</v>
-      </c>
-      <c r="D5">
-        <v>-469.6926147946568</v>
-      </c>
-      <c r="E5">
-        <v>0.1445069163394255</v>
-      </c>
-      <c r="F5">
-        <v>0.1445069183882031</v>
-      </c>
-      <c r="G5">
-        <v>93</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>958.6026208936614</v>
-      </c>
-      <c r="J5">
-        <v>1.521563080902297</v>
-      </c>
-      <c r="K5">
-        <v>3.521563080902297</v>
+      <c r="H5" s="3">
+        <v>958.60262089366142</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1.5215630809022971</v>
+      </c>
+      <c r="J5" s="3">
+        <v>3.5215630809022969</v>
       </c>
     </row>
   </sheetData>

--- a/output/models and plots/abund_best_models.xlsx
+++ b/output/models and plots/abund_best_models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB85D2E-F49E-8545-87C5-45E50C2821BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF65D57-7AB8-4B4D-A3C2-31D4FF108F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,9 +68,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -109,13 +108,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,7 +422,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -483,13 +482,13 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>955.08105781275913</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -515,13 +514,13 @@
       <c r="G3">
         <v>2</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>958.27083601834022</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>1.1897782055810919</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>3.1897782055810922</v>
       </c>
     </row>
@@ -547,13 +546,13 @@
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>958.35035853523868</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>1.2693007224795561</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>3.2693007224795561</v>
       </c>
     </row>
@@ -579,13 +578,13 @@
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>958.60262089366142</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>1.5215630809022971</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>3.5215630809022969</v>
       </c>
     </row>
